--- a/outputs/46167.xlsx
+++ b/outputs/46167.xlsx
@@ -111,16 +111,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -319,110 +323,110 @@
   <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.84"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>111111</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <f aca="false">SUMIF(A2:A12,111111,B2:B12)</f>
         <v>270</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>222222</v>
-      </c>
-      <c r="B3" s="1" t="n">
+      <c r="A3" s="2" t="n">
+        <v>222222</v>
+      </c>
+      <c r="B3" s="2" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>111111</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>222222</v>
-      </c>
-      <c r="B5" s="1" t="n">
+      <c r="A5" s="2" t="n">
+        <v>222222</v>
+      </c>
+      <c r="B5" s="2" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>222222</v>
-      </c>
-      <c r="B6" s="1" t="n">
+      <c r="A6" s="2" t="n">
+        <v>222222</v>
+      </c>
+      <c r="B6" s="2" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>111111</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
-        <v>222222</v>
-      </c>
-      <c r="B8" s="1" t="n">
+      <c r="A8" s="2" t="n">
+        <v>222222</v>
+      </c>
+      <c r="B8" s="2" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>222222</v>
-      </c>
-      <c r="B9" s="1" t="n">
+      <c r="A9" s="2" t="n">
+        <v>222222</v>
+      </c>
+      <c r="B9" s="2" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
-        <v>222222</v>
-      </c>
-      <c r="B10" s="1" t="n">
+      <c r="A10" s="2" t="n">
+        <v>222222</v>
+      </c>
+      <c r="B10" s="2" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>222222</v>
-      </c>
-      <c r="B11" s="1" t="n">
+      <c r="A11" s="2" t="n">
+        <v>222222</v>
+      </c>
+      <c r="B11" s="2" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>111111</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>90</v>
       </c>
     </row>

--- a/outputs/46167.xlsx
+++ b/outputs/46167.xlsx
@@ -346,7 +346,7 @@
         <v>50</v>
       </c>
       <c r="D2" s="1" t="n">
-        <f aca="false">SUMIF(A2:A12,111111,B2:B12)</f>
+        <f aca="false">SUMIF($A$2:$A$12,111111,$B$2:$B$12)</f>
         <v>270</v>
       </c>
     </row>
